--- a/연구코드/results/regression/external_validation_results.xlsx
+++ b/연구코드/results/regression/external_validation_results.xlsx
@@ -1,37 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>N_train</t>
+  </si>
+  <si>
+    <t>N_test</t>
+  </si>
+  <si>
+    <t>N_features_used</t>
+  </si>
+  <si>
+    <t>Lin_R2</t>
+  </si>
+  <si>
+    <t>Lin_MAE</t>
+  </si>
+  <si>
+    <t>Lin_RMSE</t>
+  </si>
+  <si>
+    <t>TAMA_threshold</t>
+  </si>
+  <si>
+    <t>Log_AUC</t>
+  </si>
+  <si>
+    <t>Log_Acc</t>
+  </si>
+  <si>
+    <t>Log_Sens</t>
+  </si>
+  <si>
+    <t>Log_Spec</t>
+  </si>
+  <si>
+    <t>강남</t>
+  </si>
+  <si>
+    <t>신촌</t>
+  </si>
+  <si>
+    <t>Case1_Clinical</t>
+  </si>
+  <si>
+    <t>Case2_Clinical+AEC_prev</t>
+  </si>
+  <si>
+    <t>Case3_Clinical+AEC_new</t>
+  </si>
+  <si>
+    <t>Case4_Clinical+AEC_prev+Scanner</t>
+  </si>
+  <si>
+    <t>Case5_Clinical+AEC_new+Scanner</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +117,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,587 +433,495 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>N_train</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>N_test</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>N_features_used</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_R2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_RMSE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TAMA_threshold</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Log_AUC</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Acc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Sens</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Spec</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Case1_Clinical</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
         <v>1365</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1269</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.6374</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>13.81</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>18.54</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>103</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.8564000000000001</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.8006</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.3885</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.9361</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Case2_Clinical+AEC_prev</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
         <v>1365</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1269</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>7</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.479</v>
       </c>
-      <c r="H3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3">
         <v>22.23</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>103</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.8496</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.8006</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.5478</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.8838</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Case3_Clinical+AEC_new</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
         <v>1365</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>1269</v>
       </c>
-      <c r="F4" t="n">
-        <v>14</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
         <v>0.5842000000000001</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>14.8</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>19.86</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>103</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.8252</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0.7887999999999999</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.5255</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.8754</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Case4_Clinical+AEC_prev+Scanner</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
         <v>1365</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1269</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>38</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.3959</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>16</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>23.93</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>103</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.8297</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0.7975</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.5541</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>0.8774999999999999</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Case5_Clinical+AEC_new+Scanner</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
         <v>1365</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>1269</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>45</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.4099</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>17.56</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>23.66</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>103</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.8122</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.7975</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>0.4745</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.9036999999999999</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Case1_Clinical</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
         <v>1269</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>1365</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>3</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.6606</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>12.82</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>17.18</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>100</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>0.8270999999999999</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0.7795</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>0.5528</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>0.8495</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Case2_Clinical+AEC_prev</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
         <v>1269</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>1365</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.6588000000000001</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>12.87</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>17.23</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>100</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>0.8259</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>0.7868000000000001</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>0.382</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>0.9118000000000001</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Case3_Clinical+AEC_new</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9">
         <v>1269</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1365</v>
       </c>
-      <c r="F9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9">
+        <v>14</v>
+      </c>
+      <c r="G9">
         <v>0.6564</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>12.97</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>17.28</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>100</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>0.823</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>0.7839</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>0.4037</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>0.9012</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Case4_Clinical+AEC_prev+Scanner</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
         <v>1269</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1365</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>38</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.6587</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>12.84</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>17.23</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>100</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>0.8294</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>0.789</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>0.528</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>0.8696</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Case5_Clinical+AEC_new+Scanner</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
         <v>1269</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1365</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>45</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.6563</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>12.92</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>17.29</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>100</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>0.8244</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>0.7897</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>0.587</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>0.8522999999999999</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/연구코드/results/regression/external_validation_results.xlsx
+++ b/연구코드/results/regression/external_validation_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t>Train</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>Case5_Clinical+AEC_new+Scanner</t>
+  </si>
+  <si>
+    <t>{'female': np.float64(95.0), 'male': np.float64(131.0)}</t>
+  </si>
+  <si>
+    <t>{'female': np.float64(95.0), 'male': np.float64(132.0)}</t>
   </si>
 </sst>
 </file>
@@ -509,20 +515,20 @@
       <c r="I2">
         <v>18.54</v>
       </c>
-      <c r="J2">
-        <v>103</v>
+      <c r="J2" t="s">
+        <v>21</v>
       </c>
       <c r="K2">
-        <v>0.8564000000000001</v>
+        <v>0.7501</v>
       </c>
       <c r="L2">
-        <v>0.8006</v>
+        <v>0.766</v>
       </c>
       <c r="M2">
-        <v>0.3885</v>
+        <v>0.246</v>
       </c>
       <c r="N2">
-        <v>0.9361</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -553,20 +559,20 @@
       <c r="I3">
         <v>22.23</v>
       </c>
-      <c r="J3">
-        <v>103</v>
+      <c r="J3" t="s">
+        <v>21</v>
       </c>
       <c r="K3">
-        <v>0.8496</v>
+        <v>0.7357</v>
       </c>
       <c r="L3">
-        <v>0.8006</v>
+        <v>0.7518</v>
       </c>
       <c r="M3">
-        <v>0.5478</v>
+        <v>0.4013</v>
       </c>
       <c r="N3">
-        <v>0.8838</v>
+        <v>0.8646</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -597,20 +603,20 @@
       <c r="I4">
         <v>19.86</v>
       </c>
-      <c r="J4">
-        <v>103</v>
+      <c r="J4" t="s">
+        <v>21</v>
       </c>
       <c r="K4">
-        <v>0.8252</v>
+        <v>0.7201</v>
       </c>
       <c r="L4">
-        <v>0.7887999999999999</v>
+        <v>0.7478</v>
       </c>
       <c r="M4">
-        <v>0.5255</v>
+        <v>0.3172</v>
       </c>
       <c r="N4">
-        <v>0.8754</v>
+        <v>0.8865</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -641,20 +647,20 @@
       <c r="I5">
         <v>23.93</v>
       </c>
-      <c r="J5">
-        <v>103</v>
+      <c r="J5" t="s">
+        <v>21</v>
       </c>
       <c r="K5">
-        <v>0.8297</v>
+        <v>0.6551</v>
       </c>
       <c r="L5">
-        <v>0.7975</v>
+        <v>0.7541</v>
       </c>
       <c r="M5">
-        <v>0.5541</v>
+        <v>0.2848</v>
       </c>
       <c r="N5">
-        <v>0.8774999999999999</v>
+        <v>0.9052</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -685,20 +691,20 @@
       <c r="I6">
         <v>23.66</v>
       </c>
-      <c r="J6">
-        <v>103</v>
+      <c r="J6" t="s">
+        <v>21</v>
       </c>
       <c r="K6">
-        <v>0.8122</v>
+        <v>0.6427</v>
       </c>
       <c r="L6">
-        <v>0.7975</v>
+        <v>0.7533</v>
       </c>
       <c r="M6">
-        <v>0.4745</v>
+        <v>0.2913</v>
       </c>
       <c r="N6">
-        <v>0.9036999999999999</v>
+        <v>0.9021</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -729,20 +735,20 @@
       <c r="I7">
         <v>17.18</v>
       </c>
-      <c r="J7">
-        <v>100</v>
+      <c r="J7" t="s">
+        <v>22</v>
       </c>
       <c r="K7">
-        <v>0.8270999999999999</v>
+        <v>0.743</v>
       </c>
       <c r="L7">
-        <v>0.7795</v>
+        <v>0.781</v>
       </c>
       <c r="M7">
-        <v>0.5528</v>
+        <v>0.1442</v>
       </c>
       <c r="N7">
-        <v>0.8495</v>
+        <v>0.9751</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -773,20 +779,20 @@
       <c r="I8">
         <v>17.23</v>
       </c>
-      <c r="J8">
-        <v>100</v>
+      <c r="J8" t="s">
+        <v>22</v>
       </c>
       <c r="K8">
-        <v>0.8259</v>
+        <v>0.7406</v>
       </c>
       <c r="L8">
-        <v>0.7868000000000001</v>
+        <v>0.7795</v>
       </c>
       <c r="M8">
-        <v>0.382</v>
+        <v>0.1473</v>
       </c>
       <c r="N8">
-        <v>0.9118000000000001</v>
+        <v>0.9723000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -817,20 +823,20 @@
       <c r="I9">
         <v>17.28</v>
       </c>
-      <c r="J9">
-        <v>100</v>
+      <c r="J9" t="s">
+        <v>22</v>
       </c>
       <c r="K9">
-        <v>0.823</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="L9">
-        <v>0.7839</v>
+        <v>0.7714</v>
       </c>
       <c r="M9">
-        <v>0.4037</v>
+        <v>0.1379</v>
       </c>
       <c r="N9">
-        <v>0.9012</v>
+        <v>0.9646</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -861,20 +867,20 @@
       <c r="I10">
         <v>17.23</v>
       </c>
-      <c r="J10">
-        <v>100</v>
+      <c r="J10" t="s">
+        <v>22</v>
       </c>
       <c r="K10">
-        <v>0.8294</v>
+        <v>0.7376</v>
       </c>
       <c r="L10">
-        <v>0.789</v>
+        <v>0.7736</v>
       </c>
       <c r="M10">
-        <v>0.528</v>
+        <v>0.1944</v>
       </c>
       <c r="N10">
-        <v>0.8696</v>
+        <v>0.9503</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -905,20 +911,20 @@
       <c r="I11">
         <v>17.29</v>
       </c>
-      <c r="J11">
-        <v>100</v>
+      <c r="J11" t="s">
+        <v>22</v>
       </c>
       <c r="K11">
-        <v>0.8244</v>
+        <v>0.7353</v>
       </c>
       <c r="L11">
-        <v>0.7897</v>
+        <v>0.7663</v>
       </c>
       <c r="M11">
-        <v>0.587</v>
+        <v>0.21</v>
       </c>
       <c r="N11">
-        <v>0.8522999999999999</v>
+        <v>0.9359</v>
       </c>
     </row>
   </sheetData>
